--- a/analysis/data/raw_data/SDG_core_metric.xlsx
+++ b/analysis/data/raw_data/SDG_core_metric.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\SPHARM_analysis\analysis\data\raw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4A33F5C-71E8-47AD-8758-2C3A26ED2EDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BA5667F-1F9C-401C-AE1A-3D1F87C7E571}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" xr2:uid="{3882E913-04A3-4E48-AF26-32C4E934CC95}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="798" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="164">
   <si>
     <t>Layer</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -407,6 +407,175 @@
   </si>
   <si>
     <t>Handaxe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SDG_L2_489</t>
+  </si>
+  <si>
+    <t>SDG_L3_1066</t>
+  </si>
+  <si>
+    <t>SDG_L3_1163</t>
+  </si>
+  <si>
+    <t>SDG_L3_1191</t>
+  </si>
+  <si>
+    <t>SDG_L3_1318</t>
+  </si>
+  <si>
+    <t>SDG_L3_1416</t>
+  </si>
+  <si>
+    <t>SDG_L3_1437</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SDG_L2_494</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SDG_L3_1492</t>
+  </si>
+  <si>
+    <t>SDG_L3_1547</t>
+  </si>
+  <si>
+    <t>SDG_L3_155</t>
+  </si>
+  <si>
+    <t>SDG_L3_1677</t>
+  </si>
+  <si>
+    <t>SDG_L3_1748</t>
+  </si>
+  <si>
+    <t>SDG_L3_188</t>
+  </si>
+  <si>
+    <t>SDG_L3_303</t>
+  </si>
+  <si>
+    <t>SDG_L3_434</t>
+  </si>
+  <si>
+    <t>SDG_L3_55</t>
+  </si>
+  <si>
+    <t>SDG_L3_636</t>
+  </si>
+  <si>
+    <t>SDG_L3_645</t>
+  </si>
+  <si>
+    <t>SDG_L3_890</t>
+  </si>
+  <si>
+    <t>SDG_L3_978</t>
+  </si>
+  <si>
+    <t>SDG_L3_804</t>
+  </si>
+  <si>
+    <t>SDG_L4_1951</t>
+  </si>
+  <si>
+    <t>SDG_L4_2001</t>
+  </si>
+  <si>
+    <t>SDG_L4_2004</t>
+  </si>
+  <si>
+    <t>SDG_L4_2158</t>
+  </si>
+  <si>
+    <t>SDG_L4_2164</t>
+  </si>
+  <si>
+    <t>SDG_L4_2165</t>
+  </si>
+  <si>
+    <t>SDG_L4_2182</t>
+  </si>
+  <si>
+    <t>SDG_L4_2213</t>
+  </si>
+  <si>
+    <t>SDG_L4_2292</t>
+  </si>
+  <si>
+    <t>SDG_L4_2389</t>
+  </si>
+  <si>
+    <t>SDG_L4_2733</t>
+  </si>
+  <si>
+    <t>SDG_L4_2527</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SDG_L4_2818</t>
+  </si>
+  <si>
+    <t>SDG_L4_3095</t>
+  </si>
+  <si>
+    <t>SDG_L4_3192</t>
+  </si>
+  <si>
+    <t>SDG_L4_3283</t>
+  </si>
+  <si>
+    <t>SDG_L4_3342</t>
+  </si>
+  <si>
+    <t>SDG_L4_3506</t>
+  </si>
+  <si>
+    <t>SDG_L4_3513</t>
+  </si>
+  <si>
+    <t>SDG_L4_3821</t>
+  </si>
+  <si>
+    <t>SDG_L4_3952</t>
+  </si>
+  <si>
+    <t>SDG_L4_3971</t>
+  </si>
+  <si>
+    <t>SDG_L4_4262</t>
+  </si>
+  <si>
+    <t>SDG_L4_4386</t>
+  </si>
+  <si>
+    <t>SDG_L4_4460</t>
+  </si>
+  <si>
+    <t>SDG_L4_4604</t>
+  </si>
+  <si>
+    <t>SDG_L4_4583</t>
+  </si>
+  <si>
+    <t>SDG_L4_1788</t>
+  </si>
+  <si>
+    <t>SDG_L4_1916</t>
+  </si>
+  <si>
+    <t>SDG_L4_1884</t>
+  </si>
+  <si>
+    <t>SDG_L4_4858</t>
+  </si>
+  <si>
+    <t>SDG_L4_3341</t>
+  </si>
+  <si>
+    <t>SDG_L4_3155</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -545,7 +714,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -596,6 +765,9 @@
     </xf>
     <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -915,7 +1087,7 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.375" customWidth="1"/>
-    <col min="2" max="2" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="14.125" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
     <col min="7" max="12" width="9.125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10.625" bestFit="1" customWidth="1"/>
@@ -1053,8 +1225,8 @@
       <c r="A2" s="12">
         <v>2</v>
       </c>
-      <c r="B2" s="12">
-        <v>489</v>
+      <c r="B2" s="12" t="s">
+        <v>109</v>
       </c>
       <c r="C2" s="12" t="s">
         <v>47</v>
@@ -1157,8 +1329,8 @@
       <c r="A3" s="12">
         <v>3</v>
       </c>
-      <c r="B3" s="12">
-        <v>55</v>
+      <c r="B3" s="12" t="s">
+        <v>125</v>
       </c>
       <c r="C3" s="12" t="s">
         <v>36</v>
@@ -1251,8 +1423,8 @@
       <c r="A4" s="12">
         <v>3</v>
       </c>
-      <c r="B4" s="12">
-        <v>155</v>
+      <c r="B4" s="12" t="s">
+        <v>119</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>47</v>
@@ -1363,8 +1535,8 @@
       <c r="A5" s="12">
         <v>3</v>
       </c>
-      <c r="B5" s="12">
-        <v>188</v>
+      <c r="B5" s="12" t="s">
+        <v>122</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>47</v>
@@ -1469,8 +1641,8 @@
       <c r="A6" s="12">
         <v>3</v>
       </c>
-      <c r="B6" s="12">
-        <v>434</v>
+      <c r="B6" s="12" t="s">
+        <v>124</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>47</v>
@@ -1567,8 +1739,8 @@
       <c r="A7" s="12">
         <v>3</v>
       </c>
-      <c r="B7" s="12">
-        <v>804</v>
+      <c r="B7" s="12" t="s">
+        <v>130</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>47</v>
@@ -1665,8 +1837,8 @@
       <c r="A8" s="12">
         <v>3</v>
       </c>
-      <c r="B8" s="12">
-        <v>890</v>
+      <c r="B8" t="s">
+        <v>128</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>47</v>
@@ -1761,8 +1933,8 @@
       <c r="A9" s="12">
         <v>3</v>
       </c>
-      <c r="B9" s="12">
-        <v>978</v>
+      <c r="B9" t="s">
+        <v>129</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>47</v>
@@ -1859,8 +2031,8 @@
       <c r="A10" s="12">
         <v>3</v>
       </c>
-      <c r="B10" s="12">
-        <v>1066</v>
+      <c r="B10" s="12" t="s">
+        <v>110</v>
       </c>
       <c r="C10" s="12" t="s">
         <v>47</v>
@@ -1953,8 +2125,8 @@
       <c r="A11" s="12">
         <v>3</v>
       </c>
-      <c r="B11" s="12">
-        <v>1416</v>
+      <c r="B11" s="12" t="s">
+        <v>114</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>47</v>
@@ -2045,8 +2217,8 @@
       <c r="A12" s="12">
         <v>3</v>
       </c>
-      <c r="B12" s="12">
-        <v>1437</v>
+      <c r="B12" s="12" t="s">
+        <v>115</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>47</v>
@@ -2153,8 +2325,8 @@
       <c r="A13" s="12">
         <v>3</v>
       </c>
-      <c r="B13" s="12">
-        <v>1492</v>
+      <c r="B13" s="12" t="s">
+        <v>117</v>
       </c>
       <c r="C13" s="12" t="s">
         <v>47</v>
@@ -2245,8 +2417,8 @@
       <c r="A14" s="12">
         <v>4</v>
       </c>
-      <c r="B14" s="12">
-        <v>2165</v>
+      <c r="B14" t="s">
+        <v>136</v>
       </c>
       <c r="C14" s="12" t="s">
         <v>47</v>
@@ -2351,8 +2523,8 @@
       <c r="A15" s="12">
         <v>4</v>
       </c>
-      <c r="B15" s="12">
-        <v>1884</v>
+      <c r="B15" t="s">
+        <v>160</v>
       </c>
       <c r="C15" s="12" t="s">
         <v>47</v>
@@ -2443,8 +2615,8 @@
       <c r="A16" s="12">
         <v>4</v>
       </c>
-      <c r="B16" s="12">
-        <v>1951</v>
+      <c r="B16" t="s">
+        <v>131</v>
       </c>
       <c r="C16" s="12" t="s">
         <v>47</v>
@@ -2535,8 +2707,8 @@
       <c r="A17" s="12">
         <v>4</v>
       </c>
-      <c r="B17" s="12">
-        <v>2001</v>
+      <c r="B17" t="s">
+        <v>132</v>
       </c>
       <c r="C17" s="12" t="s">
         <v>47</v>
@@ -2629,8 +2801,8 @@
       <c r="A18" s="12">
         <v>4</v>
       </c>
-      <c r="B18" s="12">
-        <v>2004</v>
+      <c r="B18" t="s">
+        <v>133</v>
       </c>
       <c r="C18" s="12" t="s">
         <v>47</v>
@@ -2727,8 +2899,8 @@
       <c r="A19" s="12">
         <v>4</v>
       </c>
-      <c r="B19" s="12">
-        <v>2164</v>
+      <c r="B19" t="s">
+        <v>135</v>
       </c>
       <c r="C19" s="12" t="s">
         <v>47</v>
@@ -2821,8 +2993,8 @@
       <c r="A20" s="12">
         <v>4</v>
       </c>
-      <c r="B20" s="12">
-        <v>2182</v>
+      <c r="B20" t="s">
+        <v>137</v>
       </c>
       <c r="C20" s="12" t="s">
         <v>77</v>
@@ -2931,8 +3103,8 @@
       <c r="A21" s="12">
         <v>4</v>
       </c>
-      <c r="B21" s="12">
-        <v>3971</v>
+      <c r="B21" t="s">
+        <v>152</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>47</v>
@@ -3049,8 +3221,8 @@
       <c r="A22" s="12">
         <v>4</v>
       </c>
-      <c r="B22" s="12">
-        <v>4386</v>
+      <c r="B22" t="s">
+        <v>154</v>
       </c>
       <c r="C22" s="12" t="s">
         <v>47</v>
@@ -3147,8 +3319,8 @@
       <c r="A23" s="12">
         <v>4</v>
       </c>
-      <c r="B23" s="12">
-        <v>4460</v>
+      <c r="B23" t="s">
+        <v>155</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>47</v>
@@ -3257,8 +3429,8 @@
       <c r="A24" s="12">
         <v>4</v>
       </c>
-      <c r="B24" s="12">
-        <v>4604</v>
+      <c r="B24" t="s">
+        <v>156</v>
       </c>
       <c r="C24" s="12" t="s">
         <v>47</v>
@@ -3355,8 +3527,8 @@
       <c r="A25" s="12">
         <v>3</v>
       </c>
-      <c r="B25" s="12">
-        <v>303</v>
+      <c r="B25" s="12" t="s">
+        <v>123</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>47</v>
@@ -3449,8 +3621,8 @@
       <c r="A26" s="12">
         <v>3</v>
       </c>
-      <c r="B26" s="12">
-        <v>1163</v>
+      <c r="B26" s="12" t="s">
+        <v>111</v>
       </c>
       <c r="C26" s="12" t="s">
         <v>77</v>
@@ -3517,8 +3689,8 @@
       <c r="A27" s="12">
         <v>3</v>
       </c>
-      <c r="B27" s="12">
-        <v>1677</v>
+      <c r="B27" s="12" t="s">
+        <v>120</v>
       </c>
       <c r="C27" s="12" t="s">
         <v>47</v>
@@ -3605,8 +3777,8 @@
       <c r="A28" s="12">
         <v>4</v>
       </c>
-      <c r="B28" s="12">
-        <v>2213</v>
+      <c r="B28" t="s">
+        <v>138</v>
       </c>
       <c r="C28" s="12" t="s">
         <v>47</v>
@@ -3703,8 +3875,8 @@
       <c r="A29" s="12">
         <v>4</v>
       </c>
-      <c r="B29" s="12">
-        <v>2527</v>
+      <c r="B29" t="s">
+        <v>142</v>
       </c>
       <c r="C29" s="12" t="s">
         <v>47</v>
@@ -3799,8 +3971,8 @@
       <c r="A30" s="12">
         <v>4</v>
       </c>
-      <c r="B30" s="12">
-        <v>2733</v>
+      <c r="B30" t="s">
+        <v>141</v>
       </c>
       <c r="C30" s="12" t="s">
         <v>47</v>
@@ -3893,8 +4065,8 @@
       <c r="A31" s="12">
         <v>4</v>
       </c>
-      <c r="B31" s="12">
-        <v>2818</v>
+      <c r="B31" t="s">
+        <v>143</v>
       </c>
       <c r="C31" s="12" t="s">
         <v>77</v>
@@ -3961,8 +4133,8 @@
       <c r="A32" s="12">
         <v>4</v>
       </c>
-      <c r="B32" s="12">
-        <v>3095</v>
+      <c r="B32" t="s">
+        <v>144</v>
       </c>
       <c r="C32" s="12" t="s">
         <v>47</v>
@@ -4053,8 +4225,8 @@
       <c r="A33" s="12">
         <v>4</v>
       </c>
-      <c r="B33" s="12">
-        <v>3155</v>
+      <c r="B33" s="12" t="s">
+        <v>163</v>
       </c>
       <c r="C33" s="12" t="s">
         <v>47</v>
@@ -4153,8 +4325,8 @@
       <c r="A34" s="12">
         <v>4</v>
       </c>
-      <c r="B34" s="12">
-        <v>3192</v>
+      <c r="B34" t="s">
+        <v>145</v>
       </c>
       <c r="C34" s="12" t="s">
         <v>47</v>
@@ -4253,8 +4425,8 @@
       <c r="A35" s="12">
         <v>4</v>
       </c>
-      <c r="B35" s="12">
-        <v>3283</v>
+      <c r="B35" t="s">
+        <v>146</v>
       </c>
       <c r="C35" s="12" t="s">
         <v>77</v>
@@ -4325,8 +4497,8 @@
       <c r="A36" s="12">
         <v>4</v>
       </c>
-      <c r="B36" s="12">
-        <v>3342</v>
+      <c r="B36" t="s">
+        <v>147</v>
       </c>
       <c r="C36" s="12" t="s">
         <v>47</v>
@@ -4417,8 +4589,8 @@
       <c r="A37" s="12">
         <v>4</v>
       </c>
-      <c r="B37" s="12">
-        <v>3506</v>
+      <c r="B37" t="s">
+        <v>148</v>
       </c>
       <c r="C37" s="12" t="s">
         <v>47</v>
@@ -4505,8 +4677,8 @@
       <c r="A38" s="12">
         <v>4</v>
       </c>
-      <c r="B38" s="12">
-        <v>3821</v>
+      <c r="B38" t="s">
+        <v>150</v>
       </c>
       <c r="C38" s="12" t="s">
         <v>47</v>
@@ -4589,8 +4761,8 @@
       <c r="A39" s="12">
         <v>4</v>
       </c>
-      <c r="B39" s="12">
-        <v>4262</v>
+      <c r="B39" t="s">
+        <v>153</v>
       </c>
       <c r="C39" s="12" t="s">
         <v>47</v>
@@ -4687,8 +4859,8 @@
       <c r="A40" s="12">
         <v>4</v>
       </c>
-      <c r="B40" s="12">
-        <v>4583</v>
+      <c r="B40" t="s">
+        <v>157</v>
       </c>
       <c r="C40" s="12" t="s">
         <v>47</v>
@@ -4775,8 +4947,8 @@
       <c r="A41" s="12">
         <v>3</v>
       </c>
-      <c r="B41" s="12">
-        <v>1191</v>
+      <c r="B41" s="12" t="s">
+        <v>112</v>
       </c>
       <c r="C41" s="12" t="s">
         <v>47</v>
@@ -4865,8 +5037,8 @@
       <c r="A42" s="12">
         <v>4</v>
       </c>
-      <c r="B42" s="12">
-        <v>2292</v>
+      <c r="B42" t="s">
+        <v>139</v>
       </c>
       <c r="C42" s="12" t="s">
         <v>47</v>
@@ -4957,8 +5129,8 @@
       <c r="A43" s="12">
         <v>2</v>
       </c>
-      <c r="B43" s="12">
-        <v>494</v>
+      <c r="B43" s="12" t="s">
+        <v>116</v>
       </c>
       <c r="C43" s="12" t="s">
         <v>47</v>
@@ -5051,8 +5223,8 @@
       <c r="A44" s="12">
         <v>3</v>
       </c>
-      <c r="B44" s="12">
-        <v>645</v>
+      <c r="B44" s="12" t="s">
+        <v>127</v>
       </c>
       <c r="C44" s="12" t="s">
         <v>47</v>
@@ -5143,8 +5315,8 @@
       <c r="A45" s="12">
         <v>3</v>
       </c>
-      <c r="B45" s="12">
-        <v>1547</v>
+      <c r="B45" s="12" t="s">
+        <v>118</v>
       </c>
       <c r="C45" s="12" t="s">
         <v>77</v>
@@ -5249,8 +5421,8 @@
       <c r="A46" s="12">
         <v>3</v>
       </c>
-      <c r="B46" s="12">
-        <v>1748</v>
+      <c r="B46" s="12" t="s">
+        <v>121</v>
       </c>
       <c r="C46" s="12" t="s">
         <v>77</v>
@@ -5345,8 +5517,8 @@
       <c r="A47" s="12">
         <v>4</v>
       </c>
-      <c r="B47" s="12">
-        <v>1788</v>
+      <c r="B47" s="17" t="s">
+        <v>158</v>
       </c>
       <c r="C47" s="12" t="s">
         <v>77</v>
@@ -5447,8 +5619,8 @@
       <c r="A48" s="12">
         <v>4</v>
       </c>
-      <c r="B48" s="12">
-        <v>1916</v>
+      <c r="B48" s="17" t="s">
+        <v>159</v>
       </c>
       <c r="C48" s="12" t="s">
         <v>77</v>
@@ -5543,8 +5715,8 @@
       <c r="A49" s="12">
         <v>4</v>
       </c>
-      <c r="B49" s="12">
-        <v>2158</v>
+      <c r="B49" t="s">
+        <v>134</v>
       </c>
       <c r="C49" s="12" t="s">
         <v>77</v>
@@ -5641,8 +5813,8 @@
       <c r="A50" s="12">
         <v>4</v>
       </c>
-      <c r="B50" s="12">
-        <v>2389</v>
+      <c r="B50" t="s">
+        <v>140</v>
       </c>
       <c r="C50" s="12" t="s">
         <v>77</v>
@@ -5737,8 +5909,8 @@
       <c r="A51" s="12">
         <v>4</v>
       </c>
-      <c r="B51" s="12">
-        <v>3513</v>
+      <c r="B51" t="s">
+        <v>149</v>
       </c>
       <c r="C51" s="12" t="s">
         <v>77</v>
@@ -5853,8 +6025,8 @@
       <c r="A52" s="12">
         <v>4</v>
       </c>
-      <c r="B52" s="12">
-        <v>3952</v>
+      <c r="B52" t="s">
+        <v>151</v>
       </c>
       <c r="C52" s="12" t="s">
         <v>77</v>
@@ -5949,8 +6121,8 @@
       <c r="A53" s="12">
         <v>3</v>
       </c>
-      <c r="B53" s="12">
-        <v>636</v>
+      <c r="B53" s="12" t="s">
+        <v>126</v>
       </c>
       <c r="C53" s="12" t="s">
         <v>90</v>
@@ -6027,8 +6199,8 @@
       <c r="A54" s="12">
         <v>3</v>
       </c>
-      <c r="B54" s="12">
-        <v>1318</v>
+      <c r="B54" s="12" t="s">
+        <v>113</v>
       </c>
       <c r="C54" s="12" t="s">
         <v>90</v>
@@ -6105,8 +6277,8 @@
       <c r="A55" s="12">
         <v>4</v>
       </c>
-      <c r="B55" s="12">
-        <v>3341</v>
+      <c r="B55" s="12" t="s">
+        <v>162</v>
       </c>
       <c r="C55" s="12" t="s">
         <v>77</v>
@@ -6183,8 +6355,8 @@
       <c r="A56" s="12">
         <v>4</v>
       </c>
-      <c r="B56" s="12">
-        <v>4858</v>
+      <c r="B56" s="12" t="s">
+        <v>161</v>
       </c>
       <c r="C56" s="12" t="s">
         <v>77</v>

--- a/analysis/data/raw_data/SDG_core_metric.xlsx
+++ b/analysis/data/raw_data/SDG_core_metric.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\SPHARM_analysis\analysis\data\raw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BA5667F-1F9C-401C-AE1A-3D1F87C7E571}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77EB5CE0-340E-4E25-8FEA-95E07FBED4A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" xr2:uid="{3882E913-04A3-4E48-AF26-32C4E934CC95}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3882E913-04A3-4E48-AF26-32C4E934CC95}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -386,10 +386,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Unifacial_semi_centripetal</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Unifacial_centripetal</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -576,6 +572,10 @@
   </si>
   <si>
     <t>SDG_L4_3155</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Multifacial</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1226,7 +1226,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C2" s="12" t="s">
         <v>47</v>
@@ -1330,7 +1330,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C3" s="12" t="s">
         <v>36</v>
@@ -1424,7 +1424,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>47</v>
@@ -1536,7 +1536,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>47</v>
@@ -1642,7 +1642,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>47</v>
@@ -1740,7 +1740,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>47</v>
@@ -1838,7 +1838,7 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>47</v>
@@ -1934,7 +1934,7 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>47</v>
@@ -2032,7 +2032,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C10" s="12" t="s">
         <v>47</v>
@@ -2126,7 +2126,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>47</v>
@@ -2207,7 +2207,7 @@
         <v>73</v>
       </c>
       <c r="AM11" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AN11" s="12" t="s">
         <v>46</v>
@@ -2218,7 +2218,7 @@
         <v>3</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>47</v>
@@ -2326,7 +2326,7 @@
         <v>3</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C13" s="12" t="s">
         <v>47</v>
@@ -2407,7 +2407,7 @@
         <v>73</v>
       </c>
       <c r="AM13" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AN13" s="12" t="s">
         <v>46</v>
@@ -2418,7 +2418,7 @@
         <v>4</v>
       </c>
       <c r="B14" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C14" s="12" t="s">
         <v>47</v>
@@ -2524,7 +2524,7 @@
         <v>4</v>
       </c>
       <c r="B15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C15" s="12" t="s">
         <v>47</v>
@@ -2605,7 +2605,7 @@
         <v>73</v>
       </c>
       <c r="AM15" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AN15" s="12" t="s">
         <v>46</v>
@@ -2616,7 +2616,7 @@
         <v>4</v>
       </c>
       <c r="B16" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C16" s="12" t="s">
         <v>47</v>
@@ -2708,7 +2708,7 @@
         <v>4</v>
       </c>
       <c r="B17" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C17" s="12" t="s">
         <v>47</v>
@@ -2802,7 +2802,7 @@
         <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C18" s="12" t="s">
         <v>47</v>
@@ -2900,7 +2900,7 @@
         <v>4</v>
       </c>
       <c r="B19" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C19" s="12" t="s">
         <v>47</v>
@@ -2983,7 +2983,7 @@
         <v>73</v>
       </c>
       <c r="AM19" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AN19" s="12" t="s">
         <v>58</v>
@@ -2994,7 +2994,7 @@
         <v>4</v>
       </c>
       <c r="B20" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C20" s="12" t="s">
         <v>77</v>
@@ -3104,7 +3104,7 @@
         <v>4</v>
       </c>
       <c r="B21" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>47</v>
@@ -3211,7 +3211,7 @@
         <v>79</v>
       </c>
       <c r="AM21" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AN21" s="12" t="s">
         <v>58</v>
@@ -3222,7 +3222,7 @@
         <v>4</v>
       </c>
       <c r="B22" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C22" s="12" t="s">
         <v>47</v>
@@ -3309,7 +3309,7 @@
         <v>73</v>
       </c>
       <c r="AM22" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AN22" s="12" t="s">
         <v>46</v>
@@ -3320,7 +3320,7 @@
         <v>4</v>
       </c>
       <c r="B23" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>47</v>
@@ -3430,7 +3430,7 @@
         <v>4</v>
       </c>
       <c r="B24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C24" s="12" t="s">
         <v>47</v>
@@ -3517,7 +3517,7 @@
         <v>81</v>
       </c>
       <c r="AM24" s="12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AN24" s="12" t="s">
         <v>46</v>
@@ -3528,7 +3528,7 @@
         <v>3</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>47</v>
@@ -3613,7 +3613,7 @@
         <v>82</v>
       </c>
       <c r="AM25" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AN25" s="12"/>
     </row>
@@ -3622,7 +3622,7 @@
         <v>3</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C26" s="12" t="s">
         <v>77</v>
@@ -3690,7 +3690,7 @@
         <v>3</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C27" s="12" t="s">
         <v>47</v>
@@ -3778,7 +3778,7 @@
         <v>4</v>
       </c>
       <c r="B28" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C28" s="12" t="s">
         <v>47</v>
@@ -3876,7 +3876,7 @@
         <v>4</v>
       </c>
       <c r="B29" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C29" s="12" t="s">
         <v>47</v>
@@ -3972,7 +3972,7 @@
         <v>4</v>
       </c>
       <c r="B30" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C30" s="12" t="s">
         <v>47</v>
@@ -4055,7 +4055,7 @@
         <v>82</v>
       </c>
       <c r="AM30" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AN30" s="12" t="s">
         <v>46</v>
@@ -4066,7 +4066,7 @@
         <v>4</v>
       </c>
       <c r="B31" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C31" s="12" t="s">
         <v>77</v>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="AK31" s="16"/>
       <c r="AL31" s="16" t="s">
-        <v>57</v>
+        <v>163</v>
       </c>
       <c r="AM31" s="16" t="s">
         <v>57</v>
@@ -4134,7 +4134,7 @@
         <v>4</v>
       </c>
       <c r="B32" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C32" s="12" t="s">
         <v>47</v>
@@ -4226,7 +4226,7 @@
         <v>4</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C33" s="12" t="s">
         <v>47</v>
@@ -4326,7 +4326,7 @@
         <v>4</v>
       </c>
       <c r="B34" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C34" s="12" t="s">
         <v>47</v>
@@ -4426,7 +4426,7 @@
         <v>4</v>
       </c>
       <c r="B35" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C35" s="12" t="s">
         <v>77</v>
@@ -4498,7 +4498,7 @@
         <v>4</v>
       </c>
       <c r="B36" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C36" s="12" t="s">
         <v>47</v>
@@ -4590,7 +4590,7 @@
         <v>4</v>
       </c>
       <c r="B37" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C37" s="12" t="s">
         <v>47</v>
@@ -4678,7 +4678,7 @@
         <v>4</v>
       </c>
       <c r="B38" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C38" s="12" t="s">
         <v>47</v>
@@ -4762,7 +4762,7 @@
         <v>4</v>
       </c>
       <c r="B39" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C39" s="12" t="s">
         <v>47</v>
@@ -4860,7 +4860,7 @@
         <v>4</v>
       </c>
       <c r="B40" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C40" s="12" t="s">
         <v>47</v>
@@ -4948,7 +4948,7 @@
         <v>3</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C41" s="12" t="s">
         <v>47</v>
@@ -5029,7 +5029,7 @@
       </c>
       <c r="AL41" s="16"/>
       <c r="AM41" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AN41" s="12"/>
     </row>
@@ -5038,7 +5038,7 @@
         <v>4</v>
       </c>
       <c r="B42" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C42" s="12" t="s">
         <v>47</v>
@@ -5130,7 +5130,7 @@
         <v>2</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C43" s="12" t="s">
         <v>47</v>
@@ -5224,7 +5224,7 @@
         <v>3</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C44" s="12" t="s">
         <v>47</v>
@@ -5316,7 +5316,7 @@
         <v>3</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C45" s="12" t="s">
         <v>77</v>
@@ -5422,7 +5422,7 @@
         <v>3</v>
       </c>
       <c r="B46" s="12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C46" s="12" t="s">
         <v>77</v>
@@ -5518,7 +5518,7 @@
         <v>4</v>
       </c>
       <c r="B47" s="17" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C47" s="12" t="s">
         <v>77</v>
@@ -5620,7 +5620,7 @@
         <v>4</v>
       </c>
       <c r="B48" s="17" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C48" s="12" t="s">
         <v>77</v>
@@ -5716,7 +5716,7 @@
         <v>4</v>
       </c>
       <c r="B49" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C49" s="12" t="s">
         <v>77</v>
@@ -5814,7 +5814,7 @@
         <v>4</v>
       </c>
       <c r="B50" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C50" s="12" t="s">
         <v>77</v>
@@ -5910,7 +5910,7 @@
         <v>4</v>
       </c>
       <c r="B51" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C51" s="12" t="s">
         <v>77</v>
@@ -6026,7 +6026,7 @@
         <v>4</v>
       </c>
       <c r="B52" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C52" s="12" t="s">
         <v>77</v>
@@ -6122,7 +6122,7 @@
         <v>3</v>
       </c>
       <c r="B53" s="12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C53" s="12" t="s">
         <v>90</v>
@@ -6191,7 +6191,7 @@
         <v>91</v>
       </c>
       <c r="AM53" s="12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AN53" s="12"/>
     </row>
@@ -6200,7 +6200,7 @@
         <v>3</v>
       </c>
       <c r="B54" s="12" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C54" s="12" t="s">
         <v>90</v>
@@ -6269,7 +6269,7 @@
         <v>91</v>
       </c>
       <c r="AM54" s="12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AN54" s="12"/>
     </row>
@@ -6278,7 +6278,7 @@
         <v>4</v>
       </c>
       <c r="B55" s="12" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C55" s="12" t="s">
         <v>77</v>
@@ -6347,7 +6347,7 @@
         <v>94</v>
       </c>
       <c r="AM55" s="12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AN55" s="12"/>
     </row>
@@ -6356,7 +6356,7 @@
         <v>4</v>
       </c>
       <c r="B56" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C56" s="12" t="s">
         <v>77</v>
@@ -6425,7 +6425,7 @@
         <v>95</v>
       </c>
       <c r="AM56" s="12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AN56" s="12"/>
     </row>

--- a/analysis/data/raw_data/SDG_core_metric.xlsx
+++ b/analysis/data/raw_data/SDG_core_metric.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\SPHARM_analysis\analysis\data\raw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77EB5CE0-340E-4E25-8FEA-95E07FBED4A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F109A99-7B41-4AE2-9AA7-C3874FC99B68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3882E913-04A3-4E48-AF26-32C4E934CC95}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="164">
   <si>
     <t>Layer</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1312,7 +1312,7 @@
         <v>4</v>
       </c>
       <c r="AK2" s="16">
-        <f t="shared" ref="AK2:AK7" si="1">AJ2/M2</f>
+        <f t="shared" ref="AK2:AK56" si="1">AJ2/M2</f>
         <v>4.0834457029533352E-4</v>
       </c>
       <c r="AL2" s="16" t="s">
@@ -1917,6 +1917,7 @@
         <v>4</v>
       </c>
       <c r="AK8" s="16">
+        <f t="shared" si="1"/>
         <v>2.575831530417618E-4</v>
       </c>
       <c r="AL8" s="16" t="s">
@@ -2015,6 +2016,7 @@
         <v>7</v>
       </c>
       <c r="AK9" s="16">
+        <f t="shared" si="1"/>
         <v>1.6141555724985522E-3</v>
       </c>
       <c r="AL9" s="16" t="s">
@@ -2109,6 +2111,7 @@
         <v>12</v>
       </c>
       <c r="AK10" s="16">
+        <f t="shared" si="1"/>
         <v>1.2134771441276535E-3</v>
       </c>
       <c r="AL10" s="16" t="s">
@@ -2201,6 +2204,7 @@
         <v>11</v>
       </c>
       <c r="AK11" s="16">
+        <f t="shared" si="1"/>
         <v>2.0190223104718519E-3</v>
       </c>
       <c r="AL11" s="16" t="s">
@@ -2309,6 +2313,7 @@
         <v>8</v>
       </c>
       <c r="AK12" s="16">
+        <f t="shared" si="1"/>
         <v>2.5564176612542723E-3</v>
       </c>
       <c r="AL12" s="16" t="s">
@@ -2401,6 +2406,7 @@
         <v>12</v>
       </c>
       <c r="AK13" s="16">
+        <f t="shared" si="1"/>
         <v>1.7972838727201902E-3</v>
       </c>
       <c r="AL13" s="16" t="s">
@@ -2507,6 +2513,7 @@
         <v>6</v>
       </c>
       <c r="AK14" s="16">
+        <f t="shared" si="1"/>
         <v>1.9915136954571284E-3</v>
       </c>
       <c r="AL14" s="16" t="s">
@@ -2599,6 +2606,7 @@
         <v>7</v>
       </c>
       <c r="AK15" s="16">
+        <f t="shared" si="1"/>
         <v>1.2525195997398265E-3</v>
       </c>
       <c r="AL15" s="16" t="s">
@@ -2691,6 +2699,7 @@
         <v>7</v>
       </c>
       <c r="AK16" s="16">
+        <f t="shared" si="1"/>
         <v>1.2855560232734858E-3</v>
       </c>
       <c r="AL16" s="16" t="s">
@@ -2785,6 +2794,7 @@
         <v>4</v>
       </c>
       <c r="AK17" s="16">
+        <f t="shared" si="1"/>
         <v>9.6092850293152867E-4</v>
       </c>
       <c r="AL17" s="16" t="s">
@@ -2883,6 +2893,7 @@
         <v>9</v>
       </c>
       <c r="AK18" s="16">
+        <f t="shared" si="1"/>
         <v>4.6347212905717189E-4</v>
       </c>
       <c r="AL18" s="16" t="s">
@@ -2977,6 +2988,7 @@
         <v>6</v>
       </c>
       <c r="AK19" s="16">
+        <f t="shared" si="1"/>
         <v>5.8800223193887198E-4</v>
       </c>
       <c r="AL19" s="16" t="s">
@@ -3087,6 +3099,7 @@
         <v>13</v>
       </c>
       <c r="AK20" s="16">
+        <f t="shared" si="1"/>
         <v>8.7983060418339826E-4</v>
       </c>
       <c r="AL20" s="16" t="s">
@@ -3205,6 +3218,7 @@
         <v>7</v>
       </c>
       <c r="AK21" s="16">
+        <f t="shared" si="1"/>
         <v>5.1775197329885026E-4</v>
       </c>
       <c r="AL21" s="16" t="s">
@@ -3303,6 +3317,7 @@
         <v>7</v>
       </c>
       <c r="AK22" s="16">
+        <f t="shared" si="1"/>
         <v>1.3368107217719908E-3</v>
       </c>
       <c r="AL22" s="16" t="s">
@@ -3413,6 +3428,7 @@
         <v>8</v>
       </c>
       <c r="AK23" s="16">
+        <f t="shared" si="1"/>
         <v>6.5669831999085157E-4</v>
       </c>
       <c r="AL23" s="16" t="s">
@@ -3511,6 +3527,7 @@
         <v>26</v>
       </c>
       <c r="AK24" s="16">
+        <f t="shared" si="1"/>
         <v>1.6219039981424457E-3</v>
       </c>
       <c r="AL24" s="16" t="s">
@@ -3607,6 +3624,7 @@
         <v>10</v>
       </c>
       <c r="AK25" s="16">
+        <f t="shared" si="1"/>
         <v>2.0634519735680057E-3</v>
       </c>
       <c r="AL25" s="16" t="s">
@@ -3636,8 +3654,12 @@
       <c r="F26" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
+      <c r="G26" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="H26" s="13">
+        <v>0</v>
+      </c>
       <c r="I26" s="14">
         <v>94.42</v>
       </c>
@@ -3650,8 +3672,12 @@
       <c r="L26" s="14">
         <v>760.9</v>
       </c>
-      <c r="M26" s="14"/>
-      <c r="N26" s="14"/>
+      <c r="M26" s="14">
+        <v>23761.283299999999</v>
+      </c>
+      <c r="N26" s="14">
+        <v>291005.53844999999</v>
+      </c>
       <c r="O26" s="12"/>
       <c r="P26" s="12"/>
       <c r="Q26" s="12"/>
@@ -3674,9 +3700,12 @@
       <c r="AH26" s="12"/>
       <c r="AI26" s="14"/>
       <c r="AJ26" s="15">
-        <v>0</v>
-      </c>
-      <c r="AK26" s="16"/>
+        <v>6</v>
+      </c>
+      <c r="AK26" s="16">
+        <f t="shared" si="1"/>
+        <v>2.5251161413491504E-4</v>
+      </c>
       <c r="AL26" s="16" t="s">
         <v>57</v>
       </c>
@@ -3764,7 +3793,10 @@
       <c r="AJ27" s="15">
         <v>8</v>
       </c>
-      <c r="AK27" s="16"/>
+      <c r="AK27" s="16">
+        <f t="shared" si="1"/>
+        <v>7.6171531242491444E-4</v>
+      </c>
       <c r="AL27" s="16" t="s">
         <v>45</v>
       </c>
@@ -3859,6 +3891,7 @@
         <v>7</v>
       </c>
       <c r="AK28" s="16">
+        <f t="shared" si="1"/>
         <v>8.5917950885347049E-4</v>
       </c>
       <c r="AL28" s="16" t="s">
@@ -3955,6 +3988,7 @@
         <v>8</v>
       </c>
       <c r="AK29" s="16">
+        <f t="shared" si="1"/>
         <v>2.1399239567322353E-3</v>
       </c>
       <c r="AL29" s="16" t="s">
@@ -4050,7 +4084,10 @@
       <c r="AJ30" s="15">
         <v>7</v>
       </c>
-      <c r="AK30" s="16"/>
+      <c r="AK30" s="16">
+        <f t="shared" si="1"/>
+        <v>8.8330175571618632E-4</v>
+      </c>
       <c r="AL30" s="16" t="s">
         <v>82</v>
       </c>
@@ -4094,8 +4131,12 @@
       <c r="L31" s="14">
         <v>956.8</v>
       </c>
-      <c r="M31" s="14"/>
-      <c r="N31" s="14"/>
+      <c r="M31" s="14">
+        <v>31567.2202</v>
+      </c>
+      <c r="N31" s="14">
+        <v>389664.97160300001</v>
+      </c>
       <c r="O31" s="12"/>
       <c r="P31" s="12"/>
       <c r="Q31" s="12"/>
@@ -4118,9 +4159,12 @@
       <c r="AH31" s="12"/>
       <c r="AI31" s="14"/>
       <c r="AJ31" s="15">
-        <v>0</v>
-      </c>
-      <c r="AK31" s="16"/>
+        <v>10</v>
+      </c>
+      <c r="AK31" s="16">
+        <f t="shared" si="1"/>
+        <v>3.1678430779280336E-4</v>
+      </c>
       <c r="AL31" s="16" t="s">
         <v>163</v>
       </c>
@@ -4211,6 +4255,7 @@
         <v>6</v>
       </c>
       <c r="AK32" s="16">
+        <f t="shared" si="1"/>
         <v>1.8412679142709341E-3</v>
       </c>
       <c r="AL32" s="16" t="s">
@@ -4311,6 +4356,7 @@
         <v>9</v>
       </c>
       <c r="AK33" s="16">
+        <f t="shared" si="1"/>
         <v>6.5264621608450511E-4</v>
       </c>
       <c r="AL33" s="16" t="s">
@@ -4411,6 +4457,7 @@
         <v>6</v>
       </c>
       <c r="AK34" s="16">
+        <f t="shared" si="1"/>
         <v>8.9187102813598912E-4</v>
       </c>
       <c r="AL34" s="16" t="s">
@@ -4458,8 +4505,12 @@
       <c r="L35" s="14">
         <v>1254.5</v>
       </c>
-      <c r="M35" s="14"/>
-      <c r="N35" s="14"/>
+      <c r="M35" s="14">
+        <v>36622.761700000003</v>
+      </c>
+      <c r="N35" s="14">
+        <v>487986.22839200002</v>
+      </c>
       <c r="O35" s="12"/>
       <c r="P35" s="12"/>
       <c r="Q35" s="12"/>
@@ -4482,9 +4533,12 @@
       <c r="AH35" s="12"/>
       <c r="AI35" s="14"/>
       <c r="AJ35" s="15">
-        <v>0</v>
-      </c>
-      <c r="AK35" s="16"/>
+        <v>10</v>
+      </c>
+      <c r="AK35" s="16">
+        <f t="shared" si="1"/>
+        <v>2.7305423009647031E-4</v>
+      </c>
       <c r="AL35" s="16" t="s">
         <v>57</v>
       </c>
@@ -4576,7 +4630,10 @@
       <c r="AJ36" s="15">
         <v>8</v>
       </c>
-      <c r="AK36" s="16"/>
+      <c r="AK36" s="16">
+        <f t="shared" si="1"/>
+        <v>8.7371239775285107E-4</v>
+      </c>
       <c r="AL36" s="16" t="s">
         <v>57</v>
       </c>
@@ -4663,6 +4720,7 @@
         <v>16</v>
       </c>
       <c r="AK37" s="16">
+        <f t="shared" si="1"/>
         <v>3.1864425155712982E-3</v>
       </c>
       <c r="AL37" s="16" t="s">
@@ -4747,6 +4805,7 @@
         <v>6</v>
       </c>
       <c r="AK38" s="16">
+        <f t="shared" si="1"/>
         <v>1.7493194345628144E-3</v>
       </c>
       <c r="AL38" s="16" t="s">
@@ -4794,8 +4853,12 @@
       <c r="L39" s="14">
         <v>62.2</v>
       </c>
-      <c r="M39" s="14"/>
-      <c r="N39" s="14"/>
+      <c r="M39" s="14">
+        <v>7004.2257</v>
+      </c>
+      <c r="N39" s="14">
+        <v>31456.439952000001</v>
+      </c>
       <c r="O39" s="12" t="s">
         <v>59</v>
       </c>
@@ -4844,7 +4907,10 @@
       <c r="AJ39" s="15">
         <v>7</v>
       </c>
-      <c r="AK39" s="16"/>
+      <c r="AK39" s="16">
+        <f t="shared" si="1"/>
+        <v>9.993966927707655E-4</v>
+      </c>
       <c r="AL39" s="16" t="s">
         <v>63</v>
       </c>
@@ -4933,6 +4999,7 @@
         <v>7</v>
       </c>
       <c r="AK40" s="16">
+        <f t="shared" si="1"/>
         <v>1.4230821071617421E-3</v>
       </c>
       <c r="AL40" s="16" t="s">
@@ -5025,6 +5092,7 @@
         <v>6</v>
       </c>
       <c r="AK41" s="16">
+        <f t="shared" si="1"/>
         <v>1.0830594697124223E-3</v>
       </c>
       <c r="AL41" s="16"/>
@@ -5116,7 +5184,7 @@
         <v>5</v>
       </c>
       <c r="AK42" s="16">
-        <f t="shared" ref="AK42" si="4">AJ42/M42</f>
+        <f t="shared" si="1"/>
         <v>7.937841115822961E-4</v>
       </c>
       <c r="AL42" s="16"/>
@@ -5207,6 +5275,7 @@
         <v>4</v>
       </c>
       <c r="AK43" s="16">
+        <f t="shared" si="1"/>
         <v>8.2107448598889754E-4</v>
       </c>
       <c r="AL43" s="16" t="s">
@@ -5299,6 +5368,7 @@
         <v>3</v>
       </c>
       <c r="AK44" s="16">
+        <f t="shared" si="1"/>
         <v>7.1508236711999794E-4</v>
       </c>
       <c r="AL44" s="16" t="s">
@@ -5405,6 +5475,7 @@
         <v>10</v>
       </c>
       <c r="AK45" s="16">
+        <f t="shared" si="1"/>
         <v>7.7359640403242293E-5</v>
       </c>
       <c r="AL45" s="16" t="s">
@@ -5501,6 +5572,7 @@
         <v>7</v>
       </c>
       <c r="AK46" s="16">
+        <f t="shared" si="1"/>
         <v>6.8778976730279987E-5</v>
       </c>
       <c r="AL46" s="16" t="s">
@@ -5603,6 +5675,7 @@
         <v>6</v>
       </c>
       <c r="AK47" s="16">
+        <f t="shared" si="1"/>
         <v>6.9507633560588958E-5</v>
       </c>
       <c r="AL47" s="16" t="s">
@@ -5699,6 +5772,7 @@
         <v>12</v>
       </c>
       <c r="AK48" s="16">
+        <f t="shared" si="1"/>
         <v>1.5032275912353483E-4</v>
       </c>
       <c r="AL48" s="16" t="s">
@@ -5797,6 +5871,7 @@
         <v>18</v>
       </c>
       <c r="AK49" s="16">
+        <f t="shared" si="1"/>
         <v>4.2398184928050143E-4</v>
       </c>
       <c r="AL49" s="16" t="s">
@@ -5893,6 +5968,7 @@
         <v>16</v>
       </c>
       <c r="AK50" s="16">
+        <f t="shared" si="1"/>
         <v>7.9019181911347679E-4</v>
       </c>
       <c r="AL50" s="16" t="s">
@@ -6009,6 +6085,7 @@
         <v>21</v>
       </c>
       <c r="AK51" s="16">
+        <f t="shared" si="1"/>
         <v>3.9758428319642229E-4</v>
       </c>
       <c r="AL51" s="16" t="s">
@@ -6105,6 +6182,7 @@
         <v>3</v>
       </c>
       <c r="AK52" s="16">
+        <f t="shared" si="1"/>
         <v>9.02458305448625E-5</v>
       </c>
       <c r="AL52" s="16" t="s">
@@ -6184,7 +6262,8 @@
       <c r="AJ53" s="12">
         <v>9</v>
       </c>
-      <c r="AK53" s="12">
+      <c r="AK53" s="16">
+        <f t="shared" si="1"/>
         <v>4.7595699536048754E-4</v>
       </c>
       <c r="AL53" s="12" t="s">
@@ -6262,7 +6341,8 @@
       <c r="AJ54" s="12">
         <v>9</v>
       </c>
-      <c r="AK54" s="12">
+      <c r="AK54" s="16">
+        <f t="shared" si="1"/>
         <v>1.8588465307058398E-4</v>
       </c>
       <c r="AL54" s="12" t="s">
@@ -6340,7 +6420,8 @@
       <c r="AJ55" s="12">
         <v>16</v>
       </c>
-      <c r="AK55" s="12">
+      <c r="AK55" s="16">
+        <f t="shared" si="1"/>
         <v>3.4742230218320219E-4</v>
       </c>
       <c r="AL55" s="12" t="s">
@@ -6418,7 +6499,8 @@
       <c r="AJ56" s="12">
         <v>27</v>
       </c>
-      <c r="AK56" s="12">
+      <c r="AK56" s="16">
+        <f t="shared" si="1"/>
         <v>6.2064299280671328E-4</v>
       </c>
       <c r="AL56" s="12" t="s">
